--- a/data/xlsx/bpi--gas-pipe-welding-in-energy-sector.xlsx
+++ b/data/xlsx/bpi--gas-pipe-welding-in-energy-sector.xlsx
@@ -99,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
@@ -132,6 +132,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -497,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.17" customWidth="1" min="1" max="1"/>
@@ -636,7 +642,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -660,7 +666,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -684,7 +690,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -708,7 +714,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -732,7 +738,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -756,7 +762,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -780,7 +786,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -804,7 +810,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -828,7 +834,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -852,7 +858,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -876,7 +882,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -900,7 +906,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -924,7 +930,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -948,7 +954,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -956,18 +962,18 @@
       <c r="B29" s="11" t="n"/>
       <c r="C29" s="11" t="n"/>
       <c r="D29" s="12" t="n"/>
-      <c r="E29" s="10">
+      <c r="E29" s="15">
         <f>SUM(E16:E28)</f>
         <v/>
       </c>
-      <c r="F29" s="10">
+      <c r="F29" s="15">
         <f>SUM(F16:F28)</f>
         <v/>
       </c>
       <c r="G29" s="13" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -976,7 +982,7 @@
       <c r="C30" s="11" t="n"/>
       <c r="D30" s="11" t="n"/>
       <c r="E30" s="12" t="n"/>
-      <c r="F30" s="10">
+      <c r="F30" s="15">
         <f>F29/E29*100</f>
         <v/>
       </c>
@@ -984,7 +990,7 @@
     </row>
     <row r="31" ht="9.75" customHeight="1"/>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -993,20 +999,28 @@
       <c r="C32" s="11" t="n"/>
       <c r="D32" s="11" t="n"/>
       <c r="E32" s="12" t="n"/>
-      <c r="F32" s="10">
+      <c r="F32" s="15">
         <f>F30*30/100</f>
         <v/>
       </c>
-      <c r="G32" s="10" t="inlineStr">
+      <c r="G32" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
       </c>
     </row>
+    <row r="33" ht="14.15" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>* For this course, the institute should have at least 8 welding booths. Otherwise, the total points achieved will be halved.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A33:G33"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A31:G31"/>
